--- a/artfynd/A 3949-2025 artfynd.xlsx
+++ b/artfynd/A 3949-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113280155</v>
+        <v>56091354</v>
       </c>
       <c r="B2" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>563</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Golfbanan, Västanå, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633588</v>
+        <v>633800</v>
       </c>
       <c r="R2" t="n">
-        <v>6719696</v>
+        <v>6719570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2015-05-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2015-05-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,66 +769,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113280134</v>
+        <v>81678707</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>563</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Västanå golfbana, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633593</v>
+        <v>633788</v>
       </c>
       <c r="R3" t="n">
-        <v>6719563</v>
+        <v>6719559</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2019-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2019-05-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,66 +875,66 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113280197</v>
+        <v>104729297</v>
       </c>
       <c r="B4" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219799</v>
+        <v>563</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Västanå golfbana, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633597</v>
+        <v>633659</v>
       </c>
       <c r="R4" t="n">
-        <v>6719619</v>
+        <v>6719514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,66 +981,66 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113280186</v>
+        <v>104729298</v>
       </c>
       <c r="B5" t="n">
-        <v>97558</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219788</v>
+        <v>563</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Västanå golfbana, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633689</v>
+        <v>633724</v>
       </c>
       <c r="R5" t="n">
-        <v>6719590</v>
+        <v>6719547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,66 +1087,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113280149</v>
+        <v>104729303</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>563</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Västanå golfbana, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633611</v>
+        <v>633783</v>
       </c>
       <c r="R6" t="n">
-        <v>6719562</v>
+        <v>6719569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1164,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2022-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1000-tals inom 100 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,66 +1189,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113280154</v>
+        <v>69939905</v>
       </c>
       <c r="B7" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>1262</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schkuhr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633589</v>
+        <v>633467</v>
       </c>
       <c r="R7" t="n">
-        <v>6719696</v>
+        <v>6719699</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,70 +1282,70 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113280184</v>
+        <v>69939906</v>
       </c>
       <c r="B8" t="n">
-        <v>97558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219788</v>
+        <v>1262</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Schkuhr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633605</v>
+        <v>633503</v>
       </c>
       <c r="R8" t="n">
-        <v>6719591</v>
+        <v>6719653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,12 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,74 +1388,70 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113280179</v>
+        <v>69939907</v>
       </c>
       <c r="B9" t="n">
-        <v>97558</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219788</v>
+        <v>1262</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schkuhr</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633556</v>
+        <v>633517</v>
       </c>
       <c r="R9" t="n">
-        <v>6719706</v>
+        <v>6719621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,12 +1478,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,74 +1494,70 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113280180</v>
+        <v>69939908</v>
       </c>
       <c r="B10" t="n">
-        <v>97684</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>1262</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Schkuhr</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633561</v>
+        <v>633557</v>
       </c>
       <c r="R10" t="n">
-        <v>6719707</v>
+        <v>6719553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,12 +1584,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,70 +1600,70 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113280129</v>
+        <v>69939909</v>
       </c>
       <c r="B11" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>1262</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Schkuhr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633622</v>
+        <v>633532</v>
       </c>
       <c r="R11" t="n">
-        <v>6719546</v>
+        <v>6719597</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1690,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,70 +1706,70 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113280132</v>
+        <v>69939910</v>
       </c>
       <c r="B12" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>1262</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schkuhr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633607</v>
+        <v>633517</v>
       </c>
       <c r="R12" t="n">
-        <v>6719545</v>
+        <v>6719642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,12 +1796,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,70 +1812,70 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113280148</v>
+        <v>69939911</v>
       </c>
       <c r="B13" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>1262</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schkuhr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633753</v>
+        <v>633504</v>
       </c>
       <c r="R13" t="n">
-        <v>6719665</v>
+        <v>6719669</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,12 +1902,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,70 +1918,70 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113280131</v>
+        <v>69939912</v>
       </c>
       <c r="B14" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>1262</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schkuhr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633608</v>
+        <v>633474</v>
       </c>
       <c r="R14" t="n">
-        <v>6719543</v>
+        <v>6719712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,12 +2008,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,70 +2024,86 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113280147</v>
+        <v>86248434</v>
       </c>
       <c r="B15" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>1262</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Schkuhr</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Västanåvägen Fråganbo, Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633755</v>
+        <v>633461</v>
       </c>
       <c r="R15" t="n">
-        <v>6719685</v>
+        <v>6719718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,12 +2130,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>41 blommande plantor på en sträcka av 40 m efter vägens västra sida.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,72 +2159,73 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Lennart Gårdman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Lennart Gårdman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113280183</v>
+        <v>96940285</v>
       </c>
       <c r="B16" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219799</v>
+        <v>1262</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Polygala comosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Schkuhr</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Fråganbo, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633604</v>
+        <v>633480</v>
       </c>
       <c r="R16" t="n">
-        <v>6719590</v>
+        <v>6719693</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,12 +2252,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2257,31 +2272,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113280152</v>
+        <v>113280179</v>
       </c>
       <c r="B17" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,34 +2295,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hundskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633606</v>
+        <v>633556</v>
       </c>
       <c r="R17" t="n">
-        <v>6719608</v>
+        <v>6719706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,15 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113280144</v>
+        <v>113280182</v>
       </c>
       <c r="B18" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,21 +2400,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633743</v>
+        <v>633559</v>
       </c>
       <c r="R18" t="n">
-        <v>6719705</v>
+        <v>6719713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,15 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113280130</v>
+        <v>113280184</v>
       </c>
       <c r="B19" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633616</v>
+        <v>633605</v>
       </c>
       <c r="R19" t="n">
-        <v>6719543</v>
+        <v>6719591</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,15 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113280153</v>
+        <v>113280186</v>
       </c>
       <c r="B20" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633602</v>
+        <v>633689</v>
       </c>
       <c r="R20" t="n">
-        <v>6719615</v>
+        <v>6719590</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,15 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113280151</v>
+        <v>113280129</v>
       </c>
       <c r="B21" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,21 +2703,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2727,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633593</v>
+        <v>633622</v>
       </c>
       <c r="R21" t="n">
-        <v>6719596</v>
+        <v>6719546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,15 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113280157</v>
+        <v>113280126</v>
       </c>
       <c r="B22" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,21 +2804,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2843,10 +2828,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633600</v>
+        <v>633617</v>
       </c>
       <c r="R22" t="n">
-        <v>6719731</v>
+        <v>6719535</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,15 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113280189</v>
+        <v>113280127</v>
       </c>
       <c r="B23" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,16 +2905,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2949,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633747</v>
+        <v>633621</v>
       </c>
       <c r="R23" t="n">
-        <v>6719702</v>
+        <v>6719533</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,15 +2995,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113280190</v>
+        <v>113280128</v>
       </c>
       <c r="B24" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3031,16 +3006,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3055,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633625</v>
+        <v>633623</v>
       </c>
       <c r="R24" t="n">
-        <v>6719539</v>
+        <v>6719547</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,15 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113280156</v>
+        <v>113280130</v>
       </c>
       <c r="B25" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633609</v>
+        <v>633616</v>
       </c>
       <c r="R25" t="n">
-        <v>6719712</v>
+        <v>6719543</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,15 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113280133</v>
+        <v>113280132</v>
       </c>
       <c r="B26" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3267,10 +3232,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633596</v>
+        <v>633607</v>
       </c>
       <c r="R26" t="n">
-        <v>6719538</v>
+        <v>6719545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,15 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113280135</v>
+        <v>113280133</v>
       </c>
       <c r="B27" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633586</v>
+        <v>633596</v>
       </c>
       <c r="R27" t="n">
-        <v>6719667</v>
+        <v>6719538</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,15 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113280181</v>
+        <v>113280134</v>
       </c>
       <c r="B28" t="n">
-        <v>97684</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,21 +3410,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,10 +3434,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>633561</v>
+        <v>633593</v>
       </c>
       <c r="R28" t="n">
-        <v>6719710</v>
+        <v>6719563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3545,15 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113280161</v>
+        <v>113280135</v>
       </c>
       <c r="B29" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>633563</v>
+        <v>633586</v>
       </c>
       <c r="R29" t="n">
-        <v>6719693</v>
+        <v>6719667</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,15 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113280187</v>
+        <v>113280136</v>
       </c>
       <c r="B30" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,16 +3612,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3691,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>633755</v>
+        <v>633603</v>
       </c>
       <c r="R30" t="n">
-        <v>6719672</v>
+        <v>6719681</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3757,15 +3702,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113280146</v>
+        <v>113280137</v>
       </c>
       <c r="B31" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633754</v>
+        <v>633604</v>
       </c>
       <c r="R31" t="n">
-        <v>6719689</v>
+        <v>6719694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3863,15 +3803,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113280126</v>
+        <v>113280138</v>
       </c>
       <c r="B32" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,10 +3838,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633617</v>
+        <v>633757</v>
       </c>
       <c r="R32" t="n">
-        <v>6719535</v>
+        <v>6719756</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,15 +3904,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113280128</v>
+        <v>113280139</v>
       </c>
       <c r="B33" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4009,10 +3939,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>633623</v>
+        <v>633759</v>
       </c>
       <c r="R33" t="n">
-        <v>6719547</v>
+        <v>6719751</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,15 +4005,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113280163</v>
+        <v>113280142</v>
       </c>
       <c r="B34" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,21 +4016,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4115,10 +4040,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>633584</v>
+        <v>633756</v>
       </c>
       <c r="R34" t="n">
-        <v>6719565</v>
+        <v>6719769</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,15 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113280127</v>
+        <v>113280143</v>
       </c>
       <c r="B35" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4221,10 +4141,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633621</v>
+        <v>633757</v>
       </c>
       <c r="R35" t="n">
-        <v>6719533</v>
+        <v>6719770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4287,15 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113280182</v>
+        <v>113280144</v>
       </c>
       <c r="B36" t="n">
-        <v>97558</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4303,21 +4218,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4327,10 +4242,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633559</v>
+        <v>633743</v>
       </c>
       <c r="R36" t="n">
-        <v>6719713</v>
+        <v>6719705</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,15 +4308,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113280159</v>
+        <v>113280146</v>
       </c>
       <c r="B37" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4409,21 +4319,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4343,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633590</v>
+        <v>633754</v>
       </c>
       <c r="R37" t="n">
-        <v>6719728</v>
+        <v>6719689</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,15 +4409,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113280136</v>
+        <v>113280147</v>
       </c>
       <c r="B38" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4539,10 +4444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633603</v>
+        <v>633755</v>
       </c>
       <c r="R38" t="n">
-        <v>6719681</v>
+        <v>6719685</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4605,15 +4510,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113280145</v>
+        <v>113280148</v>
       </c>
       <c r="B39" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4621,21 +4521,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4645,10 +4545,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633749</v>
+        <v>633753</v>
       </c>
       <c r="R39" t="n">
-        <v>6719691</v>
+        <v>6719665</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,15 +4611,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113280150</v>
+        <v>113280149</v>
       </c>
       <c r="B40" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4622,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633605</v>
+        <v>633611</v>
       </c>
       <c r="R40" t="n">
-        <v>6719582</v>
+        <v>6719562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,15 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113280162</v>
+        <v>113280151</v>
       </c>
       <c r="B41" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4833,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4857,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>633544</v>
+        <v>633593</v>
       </c>
       <c r="R41" t="n">
-        <v>6719632</v>
+        <v>6719596</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,15 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113280160</v>
+        <v>113280152</v>
       </c>
       <c r="B42" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4939,21 +4824,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4963,10 +4848,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>633560</v>
+        <v>633606</v>
       </c>
       <c r="R42" t="n">
-        <v>6719723</v>
+        <v>6719608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5029,15 +4914,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113280188</v>
+        <v>113280153</v>
       </c>
       <c r="B43" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5045,16 +4925,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5069,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>633755</v>
+        <v>633602</v>
       </c>
       <c r="R43" t="n">
-        <v>6719665</v>
+        <v>6719615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,15 +5015,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113280164</v>
+        <v>113280154</v>
       </c>
       <c r="B44" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,7 +5053,7 @@
         <v>633589</v>
       </c>
       <c r="R44" t="n">
-        <v>6719565</v>
+        <v>6719696</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5241,15 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113280158</v>
+        <v>113280156</v>
       </c>
       <c r="B45" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5257,21 +5127,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5281,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633606</v>
+        <v>633609</v>
       </c>
       <c r="R45" t="n">
-        <v>6719740</v>
+        <v>6719712</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5347,15 +5217,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113280137</v>
+        <v>113280161</v>
       </c>
       <c r="B46" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,10 +5252,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633604</v>
+        <v>633563</v>
       </c>
       <c r="R46" t="n">
-        <v>6719694</v>
+        <v>6719693</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5450,6 +5315,2233 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>113280164</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>633589</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6719565</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>113280183</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>633604</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6719590</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>113280187</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>633755</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6719672</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>113280188</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>633755</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6719665</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>113280189</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>633747</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6719702</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>113280190</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>633625</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6719539</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>113280197</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>633597</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6719619</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>113280131</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>633608</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6719543</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>113280140</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>633755</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6719757</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>113280141</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>633755</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6719763</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>113280145</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>633749</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6719691</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>113280150</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>633605</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6719582</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>113280155</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>633588</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6719696</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>113280157</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>633600</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6719731</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>113280158</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>633606</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6719740</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>113280159</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>633590</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6719728</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>113280160</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>633560</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6719723</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>113280162</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>633544</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6719632</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>113280163</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>633584</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6719565</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>113280180</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>633561</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6719707</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>113280181</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>633561</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6719710</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>88767660</v>
+      </c>
+      <c r="B68" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fråganbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>633490</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6719698</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3949-2025 artfynd.xlsx
+++ b/artfynd/A 3949-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091354</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729297</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729303</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939905</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939907</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939908</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,6 +1778,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939909</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939910</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939911</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69939912</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86248434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2281,6 +2356,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940285</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2386,6 +2466,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280179</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280182</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280184</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2689,6 +2784,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280186</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2790,6 +2890,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280129</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2891,6 +2996,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280126</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2992,6 +3102,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280127</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3093,6 +3208,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280128</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3194,6 +3314,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280130</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3295,6 +3420,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280132</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3396,6 +3526,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280133</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280134</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,6 +3738,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280135</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3699,6 +3844,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280136</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3800,6 +3950,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280137</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3901,6 +4056,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280138</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4002,6 +4162,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280139</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4103,6 +4268,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280142</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4204,6 +4374,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280143</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4305,6 +4480,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280144</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4406,6 +4586,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280146</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4507,6 +4692,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280147</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4608,6 +4798,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280148</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4709,6 +4904,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280149</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4810,6 +5010,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280151</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4911,6 +5116,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280152</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5012,6 +5222,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280153</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5113,6 +5328,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280154</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5214,6 +5434,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280156</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5315,6 +5540,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280161</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5416,6 +5646,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280164</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5517,6 +5752,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280183</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5618,6 +5858,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280187</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5719,6 +5964,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280188</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5820,6 +6070,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280189</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5921,6 +6176,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280190</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6022,6 +6282,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280197</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6123,6 +6388,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280131</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6224,6 +6494,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280140</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6325,6 +6600,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280141</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6426,6 +6706,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280145</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6527,6 +6812,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280150</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6628,6 +6918,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280155</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6729,6 +7024,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280157</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6830,6 +7130,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280158</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6931,6 +7236,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280159</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7032,6 +7342,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280160</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7133,6 +7448,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280162</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7234,6 +7554,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280163</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7339,6 +7664,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280180</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7440,6 +7770,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280181</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7542,8 +7877,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767660</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>